--- a/data/nzd0543/nzd0543.xlsx
+++ b/data/nzd0543/nzd0543.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H416"/>
+  <dimension ref="A1:H418"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12884,6 +12884,66 @@
       <c r="H416" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-07 22:20:52+00:00</t>
+        </is>
+      </c>
+      <c r="B417" t="n">
+        <v>277.25</v>
+      </c>
+      <c r="C417" t="n">
+        <v>256.62</v>
+      </c>
+      <c r="D417" t="n">
+        <v>235.27</v>
+      </c>
+      <c r="E417" t="n">
+        <v>215.58</v>
+      </c>
+      <c r="F417" t="n">
+        <v>207.29</v>
+      </c>
+      <c r="G417" t="n">
+        <v>198.97</v>
+      </c>
+      <c r="H417" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-08 22:15:17+00:00</t>
+        </is>
+      </c>
+      <c r="B418" t="n">
+        <v>279.87</v>
+      </c>
+      <c r="C418" t="n">
+        <v>259.21</v>
+      </c>
+      <c r="D418" t="n">
+        <v>239.08</v>
+      </c>
+      <c r="E418" t="n">
+        <v>218.79</v>
+      </c>
+      <c r="F418" t="n">
+        <v>211.05</v>
+      </c>
+      <c r="G418" t="n">
+        <v>202.81</v>
+      </c>
+      <c r="H418" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -12898,7 +12958,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B510"/>
+  <dimension ref="A1:B512"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18001,6 +18061,26 @@
       </c>
       <c r="B510" t="n">
         <v>0.8100000000000001</v>
+      </c>
+    </row>
+    <row r="511">
+      <c r="A511" t="inlineStr">
+        <is>
+          <t>2026-01-07 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B511" t="n">
+        <v>-0.37</v>
+      </c>
+    </row>
+    <row r="512">
+      <c r="A512" t="inlineStr">
+        <is>
+          <t>2026-01-08 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B512" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -18169,28 +18249,28 @@
         <v>0.0317</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.2919811973895616</v>
+        <v>-0.2904100493215739</v>
       </c>
       <c r="J2" t="n">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="K2" t="n">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="L2" t="n">
-        <v>0.03544784417431568</v>
+        <v>0.03545164736407491</v>
       </c>
       <c r="M2" t="n">
-        <v>8.798479454039724</v>
+        <v>8.762168648556548</v>
       </c>
       <c r="N2" t="n">
-        <v>126.2197744176926</v>
+        <v>125.6231093974756</v>
       </c>
       <c r="O2" t="n">
-        <v>11.23475742585004</v>
+        <v>11.20817154568378</v>
       </c>
       <c r="P2" t="n">
-        <v>284.589205218637</v>
+        <v>284.5733820064873</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -18247,28 +18327,28 @@
         <v>0.0256</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.4850127392877925</v>
+        <v>-0.4821710686126706</v>
       </c>
       <c r="J3" t="n">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="K3" t="n">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="L3" t="n">
-        <v>0.08952040691719021</v>
+        <v>0.08943835087162666</v>
       </c>
       <c r="M3" t="n">
-        <v>8.798745325127346</v>
+        <v>8.770334708061435</v>
       </c>
       <c r="N3" t="n">
-        <v>128.8121747293185</v>
+        <v>128.2371231650951</v>
       </c>
       <c r="O3" t="n">
-        <v>11.34954513314602</v>
+        <v>11.3241831124852</v>
       </c>
       <c r="P3" t="n">
-        <v>267.7003878354477</v>
+        <v>267.6716772037292</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -18325,28 +18405,28 @@
         <v>0.0259</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.3555145996099311</v>
+        <v>-0.3560587467334239</v>
       </c>
       <c r="J4" t="n">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="K4" t="n">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="L4" t="n">
-        <v>0.05304090619723967</v>
+        <v>0.0537466508642187</v>
       </c>
       <c r="M4" t="n">
-        <v>8.440755014877219</v>
+        <v>8.408800093408214</v>
       </c>
       <c r="N4" t="n">
-        <v>122.7943939564458</v>
+        <v>122.2187784501258</v>
       </c>
       <c r="O4" t="n">
-        <v>11.08126319317639</v>
+        <v>11.05526021630092</v>
       </c>
       <c r="P4" t="n">
-        <v>247.0034367543544</v>
+        <v>247.0088991298381</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -18403,28 +18483,28 @@
         <v>0.0204</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.3781524463932994</v>
+        <v>-0.3819377983935391</v>
       </c>
       <c r="J5" t="n">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="K5" t="n">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="L5" t="n">
-        <v>0.04703026167354929</v>
+        <v>0.04841555264376685</v>
       </c>
       <c r="M5" t="n">
-        <v>9.987578013907529</v>
+        <v>9.959684677339991</v>
       </c>
       <c r="N5" t="n">
-        <v>156.7467777666636</v>
+        <v>156.0755349053518</v>
       </c>
       <c r="O5" t="n">
-        <v>12.51985534128344</v>
+        <v>12.49301944708932</v>
       </c>
       <c r="P5" t="n">
-        <v>230.8926861312807</v>
+        <v>230.930751446514</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -18481,28 +18561,28 @@
         <v>0.0161</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.4022513127812847</v>
+        <v>-0.3934102141613506</v>
       </c>
       <c r="J6" t="n">
+        <v>417</v>
+      </c>
+      <c r="K6" t="n">
         <v>415</v>
       </c>
-      <c r="K6" t="n">
-        <v>413</v>
-      </c>
       <c r="L6" t="n">
-        <v>0.0390223225501023</v>
+        <v>0.03772630587783932</v>
       </c>
       <c r="M6" t="n">
-        <v>10.96302956243656</v>
+        <v>10.95086778790326</v>
       </c>
       <c r="N6" t="n">
-        <v>212.4025892939825</v>
+        <v>211.7693514069884</v>
       </c>
       <c r="O6" t="n">
-        <v>14.57403819447385</v>
+        <v>14.55229711787759</v>
       </c>
       <c r="P6" t="n">
-        <v>210.7938918521348</v>
+        <v>210.704072650816</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -18559,28 +18639,28 @@
         <v>0.016</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.0457147673468532</v>
+        <v>-0.05833671834200863</v>
       </c>
       <c r="J7" t="n">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="K7" t="n">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0009358022466795513</v>
+        <v>0.001529873397491444</v>
       </c>
       <c r="M7" t="n">
-        <v>8.303511595990893</v>
+        <v>8.330690020984445</v>
       </c>
       <c r="N7" t="n">
-        <v>120.5495715407468</v>
+        <v>120.7649659186238</v>
       </c>
       <c r="O7" t="n">
-        <v>10.97950688968985</v>
+        <v>10.98931143969556</v>
       </c>
       <c r="P7" t="n">
-        <v>214.9020106128909</v>
+        <v>215.0289206785922</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -18618,7 +18698,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H416"/>
+  <dimension ref="A1:H418"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -36021,6 +36101,90 @@
         </is>
       </c>
     </row>
+    <row r="417">
+      <c r="A417" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-07 22:20:52+00:00</t>
+        </is>
+      </c>
+      <c r="B417" t="inlineStr">
+        <is>
+          <t>-46.54103438297508,169.6150025722966</t>
+        </is>
+      </c>
+      <c r="C417" t="inlineStr">
+        <is>
+          <t>-46.54160081591289,169.6145705313886</t>
+        </is>
+      </c>
+      <c r="D417" t="inlineStr">
+        <is>
+          <t>-46.542165832888706,169.6141293270479</t>
+        </is>
+      </c>
+      <c r="E417" t="inlineStr">
+        <is>
+          <t>-46.5427340878759,169.6137092324402</t>
+        </is>
+      </c>
+      <c r="F417" t="inlineStr">
+        <is>
+          <t>-46.54332462790973,169.61343414138244</t>
+        </is>
+      </c>
+      <c r="G417" t="inlineStr">
+        <is>
+          <t>-46.54391510213251,169.61315866653973</t>
+        </is>
+      </c>
+      <c r="H417" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-08 22:15:17+00:00</t>
+        </is>
+      </c>
+      <c r="B418" t="inlineStr">
+        <is>
+          <t>-46.54103950600475,169.6150358975915</t>
+        </is>
+      </c>
+      <c r="C418" t="inlineStr">
+        <is>
+          <t>-46.54160588039822,169.61460347539438</t>
+        </is>
+      </c>
+      <c r="D418" t="inlineStr">
+        <is>
+          <t>-46.54217328313332,169.61417778951778</t>
+        </is>
+      </c>
+      <c r="E418" t="inlineStr">
+        <is>
+          <t>-46.54274036499487,169.6137500633967</t>
+        </is>
+      </c>
+      <c r="F418" t="inlineStr">
+        <is>
+          <t>-46.54333198065024,169.6134819687771</t>
+        </is>
+      </c>
+      <c r="G418" t="inlineStr">
+        <is>
+          <t>-46.5439226114206,169.61320751202763</t>
+        </is>
+      </c>
+      <c r="H418" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0543/nzd0543.xlsx
+++ b/data/nzd0543/nzd0543.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H418"/>
+  <dimension ref="A1:H419"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12944,6 +12944,36 @@
       <c r="H418" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-08 22:20:48+00:00</t>
+        </is>
+      </c>
+      <c r="B419" t="n">
+        <v>281.47</v>
+      </c>
+      <c r="C419" t="n">
+        <v>261.23</v>
+      </c>
+      <c r="D419" t="n">
+        <v>241.31</v>
+      </c>
+      <c r="E419" t="n">
+        <v>222.09</v>
+      </c>
+      <c r="F419" t="n">
+        <v>211.05</v>
+      </c>
+      <c r="G419" t="n">
+        <v>205.9</v>
+      </c>
+      <c r="H419" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -12958,7 +12988,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B512"/>
+  <dimension ref="A1:B513"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18081,6 +18111,16 @@
       </c>
       <c r="B512" t="n">
         <v>0</v>
+      </c>
+    </row>
+    <row r="513">
+      <c r="A513" t="inlineStr">
+        <is>
+          <t>2026-02-08 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B513" t="n">
+        <v>0.26</v>
       </c>
     </row>
   </sheetData>
@@ -18249,28 +18289,28 @@
         <v>0.0317</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.2904100493215739</v>
+        <v>-0.288188828705742</v>
       </c>
       <c r="J2" t="n">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="K2" t="n">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="L2" t="n">
-        <v>0.03545164736407491</v>
+        <v>0.03510405576580333</v>
       </c>
       <c r="M2" t="n">
-        <v>8.762168648556548</v>
+        <v>8.750190085601574</v>
       </c>
       <c r="N2" t="n">
-        <v>125.6231093974756</v>
+        <v>125.3655521678256</v>
       </c>
       <c r="O2" t="n">
-        <v>11.20817154568378</v>
+        <v>11.19667594278881</v>
       </c>
       <c r="P2" t="n">
-        <v>284.5733820064873</v>
+        <v>284.5509280818322</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -18327,28 +18367,28 @@
         <v>0.0256</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.4821710686126706</v>
+        <v>-0.479112413500597</v>
       </c>
       <c r="J3" t="n">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="K3" t="n">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="L3" t="n">
-        <v>0.08943835087162666</v>
+        <v>0.08879832964633461</v>
       </c>
       <c r="M3" t="n">
-        <v>8.770334708061435</v>
+        <v>8.76422704508834</v>
       </c>
       <c r="N3" t="n">
-        <v>128.2371231650951</v>
+        <v>128.0193760562981</v>
       </c>
       <c r="O3" t="n">
-        <v>11.3241831124852</v>
+        <v>11.31456477538125</v>
       </c>
       <c r="P3" t="n">
-        <v>267.6716772037292</v>
+        <v>267.6406601442664</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -18405,28 +18445,28 @@
         <v>0.0259</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.3560587467334239</v>
+        <v>-0.3542775354687561</v>
       </c>
       <c r="J4" t="n">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="K4" t="n">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0537466508642187</v>
+        <v>0.05350515704213632</v>
       </c>
       <c r="M4" t="n">
-        <v>8.408800093408214</v>
+        <v>8.398183402893888</v>
       </c>
       <c r="N4" t="n">
-        <v>122.2187784501258</v>
+        <v>121.9549931271732</v>
       </c>
       <c r="O4" t="n">
-        <v>11.05526021630092</v>
+        <v>11.04332346384788</v>
       </c>
       <c r="P4" t="n">
-        <v>247.0088991298381</v>
+        <v>246.9909474363917</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -18483,28 +18523,28 @@
         <v>0.0204</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.3819377983935391</v>
+        <v>-0.3813704446579222</v>
       </c>
       <c r="J5" t="n">
+        <v>418</v>
+      </c>
+      <c r="K5" t="n">
         <v>417</v>
       </c>
-      <c r="K5" t="n">
-        <v>416</v>
-      </c>
       <c r="L5" t="n">
-        <v>0.04841555264376685</v>
+        <v>0.04853324809381887</v>
       </c>
       <c r="M5" t="n">
-        <v>9.959684677339991</v>
+        <v>9.938286868562793</v>
       </c>
       <c r="N5" t="n">
-        <v>156.0755349053518</v>
+        <v>155.7044141962964</v>
       </c>
       <c r="O5" t="n">
-        <v>12.49301944708932</v>
+        <v>12.4781574840317</v>
       </c>
       <c r="P5" t="n">
-        <v>230.930751446514</v>
+        <v>230.9250247576771</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -18561,28 +18601,28 @@
         <v>0.0161</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.3934102141613506</v>
+        <v>-0.3881060099481885</v>
       </c>
       <c r="J6" t="n">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="K6" t="n">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="L6" t="n">
-        <v>0.03772630587783932</v>
+        <v>0.03690571487684902</v>
       </c>
       <c r="M6" t="n">
-        <v>10.95086778790326</v>
+        <v>10.94870024991626</v>
       </c>
       <c r="N6" t="n">
-        <v>211.7693514069884</v>
+        <v>211.5306685286457</v>
       </c>
       <c r="O6" t="n">
-        <v>14.55229711787759</v>
+        <v>14.54409393976283</v>
       </c>
       <c r="P6" t="n">
-        <v>210.704072650816</v>
+        <v>210.6499885249121</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -18639,28 +18679,28 @@
         <v>0.016</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.05833671834200863</v>
+        <v>-0.06207661909683272</v>
       </c>
       <c r="J7" t="n">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="K7" t="n">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="L7" t="n">
-        <v>0.001529873397491444</v>
+        <v>0.001739615539432138</v>
       </c>
       <c r="M7" t="n">
-        <v>8.330690020984445</v>
+        <v>8.330526604459981</v>
       </c>
       <c r="N7" t="n">
-        <v>120.7649659186238</v>
+        <v>120.6131126323715</v>
       </c>
       <c r="O7" t="n">
-        <v>10.98931143969556</v>
+        <v>10.98240013077157</v>
       </c>
       <c r="P7" t="n">
-        <v>215.0289206785922</v>
+        <v>215.0666643294767</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -18698,7 +18738,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H418"/>
+  <dimension ref="A1:H419"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -36185,6 +36225,48 @@
         </is>
       </c>
     </row>
+    <row r="419">
+      <c r="A419" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-08 22:20:48+00:00</t>
+        </is>
+      </c>
+      <c r="B419" t="inlineStr">
+        <is>
+          <t>-46.5410426345678,169.61505624892</t>
+        </is>
+      </c>
+      <c r="C419" t="inlineStr">
+        <is>
+          <t>-46.54160983029922,169.61462916917952</t>
+        </is>
+      </c>
+      <c r="D419" t="inlineStr">
+        <is>
+          <t>-46.542177643765804,169.61420615469711</t>
+        </is>
+      </c>
+      <c r="E419" t="inlineStr">
+        <is>
+          <t>-46.54274681809287,169.613792039157</t>
+        </is>
+      </c>
+      <c r="F419" t="inlineStr">
+        <is>
+          <t>-46.54333198065024,169.6134819687771</t>
+        </is>
+      </c>
+      <c r="G419" t="inlineStr">
+        <is>
+          <t>-46.543928654035945,169.6132468173918</t>
+        </is>
+      </c>
+      <c r="H419" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0543/nzd0543.xlsx
+++ b/data/nzd0543/nzd0543.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H419"/>
+  <dimension ref="A1:H420"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12972,6 +12972,36 @@
         <v>205.9</v>
       </c>
       <c r="H419" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-05 22:14:55+00:00</t>
+        </is>
+      </c>
+      <c r="B420" t="n">
+        <v>285.45</v>
+      </c>
+      <c r="C420" t="n">
+        <v>265.31</v>
+      </c>
+      <c r="D420" t="n">
+        <v>246.99</v>
+      </c>
+      <c r="E420" t="n">
+        <v>228.43</v>
+      </c>
+      <c r="F420" t="n">
+        <v>217.02</v>
+      </c>
+      <c r="G420" t="n">
+        <v>206.14</v>
+      </c>
+      <c r="H420" t="inlineStr">
         <is>
           <t>L8</t>
         </is>
@@ -12988,7 +13018,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B513"/>
+  <dimension ref="A1:B514"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18121,6 +18151,16 @@
       </c>
       <c r="B513" t="n">
         <v>0.26</v>
+      </c>
+    </row>
+    <row r="514">
+      <c r="A514" t="inlineStr">
+        <is>
+          <t>2026-03-05 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B514" t="n">
+        <v>-0.89</v>
       </c>
     </row>
   </sheetData>
@@ -18289,28 +18329,28 @@
         <v>0.0317</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.288188828705742</v>
+        <v>-0.2840130438627616</v>
       </c>
       <c r="J2" t="n">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="K2" t="n">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="L2" t="n">
-        <v>0.03510405576580333</v>
+        <v>0.03426603845295606</v>
       </c>
       <c r="M2" t="n">
-        <v>8.750190085601574</v>
+        <v>8.746401374284432</v>
       </c>
       <c r="N2" t="n">
-        <v>125.3655521678256</v>
+        <v>125.2333566996957</v>
       </c>
       <c r="O2" t="n">
-        <v>11.19667594278881</v>
+        <v>11.19077105027601</v>
       </c>
       <c r="P2" t="n">
-        <v>284.5509280818322</v>
+        <v>284.508589921512</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -18367,28 +18407,28 @@
         <v>0.0256</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.479112413500597</v>
+        <v>-0.4740504789497237</v>
       </c>
       <c r="J3" t="n">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="K3" t="n">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="L3" t="n">
-        <v>0.08879832964633461</v>
+        <v>0.08738179570797777</v>
       </c>
       <c r="M3" t="n">
-        <v>8.76422704508834</v>
+        <v>8.76782259339142</v>
       </c>
       <c r="N3" t="n">
-        <v>128.0193760562981</v>
+        <v>127.9619095482838</v>
       </c>
       <c r="O3" t="n">
-        <v>11.31456477538125</v>
+        <v>11.31202499768648</v>
       </c>
       <c r="P3" t="n">
-        <v>267.6406601442664</v>
+        <v>267.5891782053544</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -18445,28 +18485,28 @@
         <v>0.0259</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.3542775354687561</v>
+        <v>-0.3497133072878437</v>
       </c>
       <c r="J4" t="n">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="K4" t="n">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="L4" t="n">
-        <v>0.05350515704213632</v>
+        <v>0.05239738325181476</v>
       </c>
       <c r="M4" t="n">
-        <v>8.398183402893888</v>
+        <v>8.40286950805768</v>
       </c>
       <c r="N4" t="n">
-        <v>121.9549931271732</v>
+        <v>121.8677560755918</v>
       </c>
       <c r="O4" t="n">
-        <v>11.04332346384788</v>
+        <v>11.03937299286476</v>
       </c>
       <c r="P4" t="n">
-        <v>246.9909474363917</v>
+        <v>246.9448111463986</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -18523,28 +18563,28 @@
         <v>0.0204</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.3813704446579222</v>
+        <v>-0.3776805423856442</v>
       </c>
       <c r="J5" t="n">
+        <v>419</v>
+      </c>
+      <c r="K5" t="n">
         <v>418</v>
       </c>
-      <c r="K5" t="n">
-        <v>417</v>
-      </c>
       <c r="L5" t="n">
-        <v>0.04853324809381887</v>
+        <v>0.04785658580963081</v>
       </c>
       <c r="M5" t="n">
-        <v>9.938286868562793</v>
+        <v>9.93062004558506</v>
       </c>
       <c r="N5" t="n">
-        <v>155.7044141962964</v>
+        <v>155.4658037565034</v>
       </c>
       <c r="O5" t="n">
-        <v>12.4781574840317</v>
+        <v>12.46859269350408</v>
       </c>
       <c r="P5" t="n">
-        <v>230.9250247576771</v>
+        <v>230.8876709293969</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -18601,28 +18641,28 @@
         <v>0.0161</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.3881060099481885</v>
+        <v>-0.379872970442384</v>
       </c>
       <c r="J6" t="n">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="K6" t="n">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="L6" t="n">
-        <v>0.03690571487684902</v>
+        <v>0.03549716210592968</v>
       </c>
       <c r="M6" t="n">
-        <v>10.94870024991626</v>
+        <v>10.96032190756656</v>
       </c>
       <c r="N6" t="n">
-        <v>211.5306685286457</v>
+        <v>211.6756844236719</v>
       </c>
       <c r="O6" t="n">
-        <v>14.54409393976283</v>
+        <v>14.54907847334916</v>
       </c>
       <c r="P6" t="n">
-        <v>210.6499885249121</v>
+        <v>210.5657982749227</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -18679,28 +18719,28 @@
         <v>0.016</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.06207661909683272</v>
+        <v>-0.06566071241082011</v>
       </c>
       <c r="J7" t="n">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="K7" t="n">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="L7" t="n">
-        <v>0.001739615539432138</v>
+        <v>0.00195467771376967</v>
       </c>
       <c r="M7" t="n">
-        <v>8.330526604459981</v>
+        <v>8.329542590039429</v>
       </c>
       <c r="N7" t="n">
-        <v>120.6131126323715</v>
+        <v>120.4512985474991</v>
       </c>
       <c r="O7" t="n">
-        <v>10.98240013077157</v>
+        <v>10.97503068549237</v>
       </c>
       <c r="P7" t="n">
-        <v>215.0666643294767</v>
+        <v>215.102941180746</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -18738,7 +18778,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H419"/>
+  <dimension ref="A1:H420"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -36267,6 +36307,48 @@
         </is>
       </c>
     </row>
+    <row r="420">
+      <c r="A420" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-05 22:14:55+00:00</t>
+        </is>
+      </c>
+      <c r="B420" t="inlineStr">
+        <is>
+          <t>-46.541050416852904,169.61510687286062</t>
+        </is>
+      </c>
+      <c r="C420" t="inlineStr">
+        <is>
+          <t>-46.541617808299755,169.61468106554997</t>
+        </is>
+      </c>
+      <c r="D420" t="inlineStr">
+        <is>
+          <t>-46.54218875063698,169.61427840324788</t>
+        </is>
+      </c>
+      <c r="E420" t="inlineStr">
+        <is>
+          <t>-46.54275921582039,169.61387268352675</t>
+        </is>
+      </c>
+      <c r="F420" t="inlineStr">
+        <is>
+          <t>-46.543343655040836,169.61355790751495</t>
+        </is>
+      </c>
+      <c r="G420" t="inlineStr">
+        <is>
+          <t>-46.54392912336475,169.613249870236</t>
+        </is>
+      </c>
+      <c r="H420" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0543/nzd0543.xlsx
+++ b/data/nzd0543/nzd0543.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H420"/>
+  <dimension ref="A1:H422"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12906,7 +12906,7 @@
         <v>215.58</v>
       </c>
       <c r="F417" t="n">
-        <v>207.29</v>
+        <v>196.5</v>
       </c>
       <c r="G417" t="n">
         <v>198.97</v>
@@ -12936,7 +12936,7 @@
         <v>218.79</v>
       </c>
       <c r="F418" t="n">
-        <v>211.05</v>
+        <v>196.5</v>
       </c>
       <c r="G418" t="n">
         <v>202.81</v>
@@ -12966,7 +12966,7 @@
         <v>222.09</v>
       </c>
       <c r="F419" t="n">
-        <v>211.05</v>
+        <v>196.5</v>
       </c>
       <c r="G419" t="n">
         <v>205.9</v>
@@ -12996,12 +12996,72 @@
         <v>228.43</v>
       </c>
       <c r="F420" t="n">
-        <v>217.02</v>
+        <v>195.89</v>
       </c>
       <c r="G420" t="n">
         <v>206.14</v>
       </c>
       <c r="H420" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-29 22:14:55+00:00</t>
+        </is>
+      </c>
+      <c r="B421" t="n">
+        <v>285.48</v>
+      </c>
+      <c r="C421" t="n">
+        <v>263.75</v>
+      </c>
+      <c r="D421" t="n">
+        <v>246.41</v>
+      </c>
+      <c r="E421" t="n">
+        <v>227.99</v>
+      </c>
+      <c r="F421" t="n">
+        <v>195.71</v>
+      </c>
+      <c r="G421" t="n">
+        <v>211.18</v>
+      </c>
+      <c r="H421" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-13 22:20:21+00:00</t>
+        </is>
+      </c>
+      <c r="B422" t="n">
+        <v>286.5</v>
+      </c>
+      <c r="C422" t="n">
+        <v>264.81</v>
+      </c>
+      <c r="D422" t="n">
+        <v>247.06</v>
+      </c>
+      <c r="E422" t="n">
+        <v>227.42</v>
+      </c>
+      <c r="F422" t="n">
+        <v>188.85</v>
+      </c>
+      <c r="G422" t="n">
+        <v>217.8</v>
+      </c>
+      <c r="H422" t="inlineStr">
         <is>
           <t>L8</t>
         </is>
@@ -13018,7 +13078,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B514"/>
+  <dimension ref="A1:B516"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18161,6 +18221,26 @@
       </c>
       <c r="B514" t="n">
         <v>-0.89</v>
+      </c>
+    </row>
+    <row r="515">
+      <c r="A515" t="inlineStr">
+        <is>
+          <t>2026-03-29 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B515" t="n">
+        <v>0.17</v>
+      </c>
+    </row>
+    <row r="516">
+      <c r="A516" t="inlineStr">
+        <is>
+          <t>2026-04-13 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B516" t="n">
+        <v>0.43</v>
       </c>
     </row>
   </sheetData>
@@ -18329,28 +18409,28 @@
         <v>0.0317</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.2840130438627616</v>
+        <v>-0.2752460756990218</v>
       </c>
       <c r="J2" t="n">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="K2" t="n">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="L2" t="n">
-        <v>0.03426603845295606</v>
+        <v>0.03250132793831162</v>
       </c>
       <c r="M2" t="n">
-        <v>8.746401374284432</v>
+        <v>8.740310835998425</v>
       </c>
       <c r="N2" t="n">
-        <v>125.2333566996957</v>
+        <v>125.0104131087245</v>
       </c>
       <c r="O2" t="n">
-        <v>11.19077105027601</v>
+        <v>11.18080556618013</v>
       </c>
       <c r="P2" t="n">
-        <v>284.508589921512</v>
+        <v>284.4193662207841</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -18407,28 +18487,28 @@
         <v>0.0256</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.4740504789497237</v>
+        <v>-0.4650594581417906</v>
       </c>
       <c r="J3" t="n">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="K3" t="n">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="L3" t="n">
-        <v>0.08738179570797777</v>
+        <v>0.08499675781186655</v>
       </c>
       <c r="M3" t="n">
-        <v>8.76782259339142</v>
+        <v>8.769263537185452</v>
       </c>
       <c r="N3" t="n">
-        <v>127.9619095482838</v>
+        <v>127.7472333297539</v>
       </c>
       <c r="O3" t="n">
-        <v>11.31202499768648</v>
+        <v>11.30253216450871</v>
       </c>
       <c r="P3" t="n">
-        <v>267.5891782053544</v>
+        <v>267.497397126259</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -18485,28 +18565,28 @@
         <v>0.0259</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.3497133072878437</v>
+        <v>-0.340947684651621</v>
       </c>
       <c r="J4" t="n">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="K4" t="n">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="L4" t="n">
-        <v>0.05239738325181476</v>
+        <v>0.05031038996908788</v>
       </c>
       <c r="M4" t="n">
-        <v>8.40286950805768</v>
+        <v>8.410020401382688</v>
       </c>
       <c r="N4" t="n">
-        <v>121.8677560755918</v>
+        <v>121.6662202612054</v>
       </c>
       <c r="O4" t="n">
-        <v>11.03937299286476</v>
+        <v>11.03024116967555</v>
       </c>
       <c r="P4" t="n">
-        <v>246.9448111463986</v>
+        <v>246.8558752478936</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -18563,28 +18643,28 @@
         <v>0.0204</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.3776805423856442</v>
+        <v>-0.3710958603979377</v>
       </c>
       <c r="J5" t="n">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="K5" t="n">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="L5" t="n">
-        <v>0.04785658580963081</v>
+        <v>0.04671003379692706</v>
       </c>
       <c r="M5" t="n">
-        <v>9.93062004558506</v>
+        <v>9.911725361009502</v>
       </c>
       <c r="N5" t="n">
-        <v>155.4658037565034</v>
+        <v>154.9398778030764</v>
       </c>
       <c r="O5" t="n">
-        <v>12.46859269350408</v>
+        <v>12.44748479826653</v>
       </c>
       <c r="P5" t="n">
-        <v>230.8876709293969</v>
+        <v>230.820770949702</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -18641,28 +18721,28 @@
         <v>0.0161</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.379872970442384</v>
+        <v>-0.4177024506363475</v>
       </c>
       <c r="J6" t="n">
+        <v>421</v>
+      </c>
+      <c r="K6" t="n">
         <v>419</v>
       </c>
-      <c r="K6" t="n">
-        <v>417</v>
-      </c>
       <c r="L6" t="n">
-        <v>0.03549716210592968</v>
+        <v>0.04322236769104237</v>
       </c>
       <c r="M6" t="n">
-        <v>10.96032190756656</v>
+        <v>10.88050520134215</v>
       </c>
       <c r="N6" t="n">
-        <v>211.6756844236719</v>
+        <v>209.8461367048133</v>
       </c>
       <c r="O6" t="n">
-        <v>14.54907847334916</v>
+        <v>14.48606698537644</v>
       </c>
       <c r="P6" t="n">
-        <v>210.5657982749227</v>
+        <v>210.9519003915493</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -18719,28 +18799,28 @@
         <v>0.016</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.06566071241082011</v>
+        <v>-0.06457200951448913</v>
       </c>
       <c r="J7" t="n">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="K7" t="n">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="L7" t="n">
-        <v>0.00195467771376967</v>
+        <v>0.001910694460706686</v>
       </c>
       <c r="M7" t="n">
-        <v>8.329542590039429</v>
+        <v>8.305229817558949</v>
       </c>
       <c r="N7" t="n">
-        <v>120.4512985474991</v>
+        <v>119.9369319003038</v>
       </c>
       <c r="O7" t="n">
-        <v>10.97503068549237</v>
+        <v>10.9515721200339</v>
       </c>
       <c r="P7" t="n">
-        <v>215.102941180746</v>
+        <v>215.0918529450863</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -18778,7 +18858,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H420"/>
+  <dimension ref="A1:H422"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -36209,7 +36289,7 @@
       </c>
       <c r="F417" t="inlineStr">
         <is>
-          <t>-46.54332462790973,169.61343414138244</t>
+          <t>-46.54330352778177,169.61329689210157</t>
         </is>
       </c>
       <c r="G417" t="inlineStr">
@@ -36251,7 +36331,7 @@
       </c>
       <c r="F418" t="inlineStr">
         <is>
-          <t>-46.54333198065024,169.6134819687771</t>
+          <t>-46.54330352778177,169.61329689210157</t>
         </is>
       </c>
       <c r="G418" t="inlineStr">
@@ -36293,7 +36373,7 @@
       </c>
       <c r="F419" t="inlineStr">
         <is>
-          <t>-46.54333198065024,169.6134819687771</t>
+          <t>-46.54330352778177,169.61329689210157</t>
         </is>
       </c>
       <c r="G419" t="inlineStr">
@@ -36335,7 +36415,7 @@
       </c>
       <c r="F420" t="inlineStr">
         <is>
-          <t>-46.543343655040836,169.61355790751495</t>
+          <t>-46.54330233490594,169.61328913287784</t>
         </is>
       </c>
       <c r="G420" t="inlineStr">
@@ -36344,6 +36424,90 @@
         </is>
       </c>
       <c r="H420" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-29 22:14:55+00:00</t>
+        </is>
+      </c>
+      <c r="B421" t="inlineStr">
+        <is>
+          <t>-46.54105047551326,169.61510725444816</t>
+        </is>
+      </c>
+      <c r="C421" t="inlineStr">
+        <is>
+          <t>-46.54161475789053,169.61466122281814</t>
+        </is>
+      </c>
+      <c r="D421" t="inlineStr">
+        <is>
+          <t>-46.542187616486714,169.61427102575354</t>
+        </is>
+      </c>
+      <c r="E421" t="inlineStr">
+        <is>
+          <t>-46.54275835541209,169.6138670867553</t>
+        </is>
+      </c>
+      <c r="F421" t="inlineStr">
+        <is>
+          <t>-46.543301982909675,169.61328684327088</t>
+        </is>
+      </c>
+      <c r="G421" t="inlineStr">
+        <is>
+          <t>-46.54393897925081,169.61331397997762</t>
+        </is>
+      </c>
+      <c r="H421" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-13 22:20:21+00:00</t>
+        </is>
+      </c>
+      <c r="B422" t="inlineStr">
+        <is>
+          <t>-46.54105246996464,169.61512022842544</t>
+        </is>
+      </c>
+      <c r="C422" t="inlineStr">
+        <is>
+          <t>-46.541616830604866,169.6146747056998</t>
+        </is>
+      </c>
+      <c r="D422" t="inlineStr">
+        <is>
+          <t>-46.54218888751715,169.61427929363512</t>
+        </is>
+      </c>
+      <c r="E422" t="inlineStr">
+        <is>
+          <t>-46.54275724079185,169.61385983639263</t>
+        </is>
+      </c>
+      <c r="F422" t="inlineStr">
+        <is>
+          <t>-46.5432885679079,169.6131995838305</t>
+        </is>
+      </c>
+      <c r="G422" t="inlineStr">
+        <is>
+          <t>-46.54395192482518,169.6133981876527</t>
+        </is>
+      </c>
+      <c r="H422" t="inlineStr">
         <is>
           <t>L8</t>
         </is>

--- a/data/nzd0543/nzd0543.xlsx
+++ b/data/nzd0543/nzd0543.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H422"/>
+  <dimension ref="A1:H426"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13023,7 +13023,7 @@
         <v>246.41</v>
       </c>
       <c r="E421" t="n">
-        <v>227.99</v>
+        <v>233.29</v>
       </c>
       <c r="F421" t="n">
         <v>195.71</v>
@@ -13053,7 +13053,7 @@
         <v>247.06</v>
       </c>
       <c r="E422" t="n">
-        <v>227.42</v>
+        <v>238.12</v>
       </c>
       <c r="F422" t="n">
         <v>188.85</v>
@@ -13062,6 +13062,126 @@
         <v>217.8</v>
       </c>
       <c r="H422" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-22 22:14:08+00:00</t>
+        </is>
+      </c>
+      <c r="B423" t="n">
+        <v>286.75</v>
+      </c>
+      <c r="C423" t="n">
+        <v>265.2</v>
+      </c>
+      <c r="D423" t="n">
+        <v>248.36</v>
+      </c>
+      <c r="E423" t="n">
+        <v>239.68</v>
+      </c>
+      <c r="F423" t="n">
+        <v>199.41</v>
+      </c>
+      <c r="G423" t="n">
+        <v>218.15</v>
+      </c>
+      <c r="H423" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-29 22:20:17+00:00</t>
+        </is>
+      </c>
+      <c r="B424" t="n">
+        <v>282.24</v>
+      </c>
+      <c r="C424" t="n">
+        <v>263.15</v>
+      </c>
+      <c r="D424" t="n">
+        <v>247.35</v>
+      </c>
+      <c r="E424" t="n">
+        <v>239.78</v>
+      </c>
+      <c r="F424" t="n">
+        <v>193.94</v>
+      </c>
+      <c r="G424" t="n">
+        <v>218.2</v>
+      </c>
+      <c r="H424" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-30 22:14:17+00:00</t>
+        </is>
+      </c>
+      <c r="B425" t="n">
+        <v>282.24</v>
+      </c>
+      <c r="C425" t="n">
+        <v>262.53</v>
+      </c>
+      <c r="D425" t="n">
+        <v>248.09</v>
+      </c>
+      <c r="E425" t="n">
+        <v>237.51</v>
+      </c>
+      <c r="F425" t="n">
+        <v>193.94</v>
+      </c>
+      <c r="G425" t="n">
+        <v>218.03</v>
+      </c>
+      <c r="H425" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-15 22:19:54+00:00</t>
+        </is>
+      </c>
+      <c r="B426" t="n">
+        <v>284.07</v>
+      </c>
+      <c r="C426" t="n">
+        <v>263.81</v>
+      </c>
+      <c r="D426" t="n">
+        <v>249.83</v>
+      </c>
+      <c r="E426" t="n">
+        <v>241.02</v>
+      </c>
+      <c r="F426" t="n">
+        <v>200.15</v>
+      </c>
+      <c r="G426" t="n">
+        <v>220.42</v>
+      </c>
+      <c r="H426" t="inlineStr">
         <is>
           <t>L8</t>
         </is>
@@ -13078,7 +13198,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B516"/>
+  <dimension ref="A1:B520"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18241,6 +18361,46 @@
       </c>
       <c r="B516" t="n">
         <v>0.43</v>
+      </c>
+    </row>
+    <row r="517">
+      <c r="A517" t="inlineStr">
+        <is>
+          <t>2026-04-22 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B517" t="n">
+        <v>0.11</v>
+      </c>
+    </row>
+    <row r="518">
+      <c r="A518" t="inlineStr">
+        <is>
+          <t>2026-04-29 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B518" t="n">
+        <v>-0.16</v>
+      </c>
+    </row>
+    <row r="519">
+      <c r="A519" t="inlineStr">
+        <is>
+          <t>2026-04-30 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B519" t="n">
+        <v>-0.48</v>
+      </c>
+    </row>
+    <row r="520">
+      <c r="A520" t="inlineStr">
+        <is>
+          <t>2026-05-15 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B520" t="n">
+        <v>-0.23</v>
       </c>
     </row>
   </sheetData>
@@ -18409,28 +18569,28 @@
         <v>0.0317</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.2752460756990218</v>
+        <v>-0.2625149074113793</v>
       </c>
       <c r="J2" t="n">
-        <v>421</v>
+        <v>425</v>
       </c>
       <c r="K2" t="n">
-        <v>413</v>
+        <v>417</v>
       </c>
       <c r="L2" t="n">
-        <v>0.03250132793831162</v>
+        <v>0.03017853447369723</v>
       </c>
       <c r="M2" t="n">
-        <v>8.740310835998425</v>
+        <v>8.709209139105356</v>
       </c>
       <c r="N2" t="n">
-        <v>125.0104131087245</v>
+        <v>124.2573499478782</v>
       </c>
       <c r="O2" t="n">
-        <v>11.18080556618013</v>
+        <v>11.14707809014892</v>
       </c>
       <c r="P2" t="n">
-        <v>284.4193662207841</v>
+        <v>284.2894174017837</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -18487,28 +18647,28 @@
         <v>0.0256</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.4650594581417906</v>
+        <v>-0.4489038859990397</v>
       </c>
       <c r="J3" t="n">
-        <v>421</v>
+        <v>425</v>
       </c>
       <c r="K3" t="n">
-        <v>418</v>
+        <v>422</v>
       </c>
       <c r="L3" t="n">
-        <v>0.08499675781186655</v>
+        <v>0.08088274186569389</v>
       </c>
       <c r="M3" t="n">
-        <v>8.769263537185452</v>
+        <v>8.764775374122062</v>
       </c>
       <c r="N3" t="n">
-        <v>127.7472333297539</v>
+        <v>127.2017848475874</v>
       </c>
       <c r="O3" t="n">
-        <v>11.30253216450871</v>
+        <v>11.2783768711454</v>
       </c>
       <c r="P3" t="n">
-        <v>267.497397126259</v>
+        <v>267.3319972143256</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -18565,28 +18725,28 @@
         <v>0.0259</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.340947684651621</v>
+        <v>-0.3209041048073187</v>
       </c>
       <c r="J4" t="n">
+        <v>425</v>
+      </c>
+      <c r="K4" t="n">
         <v>421</v>
       </c>
-      <c r="K4" t="n">
-        <v>417</v>
-      </c>
       <c r="L4" t="n">
-        <v>0.05031038996908788</v>
+        <v>0.04539584538247987</v>
       </c>
       <c r="M4" t="n">
-        <v>8.410020401382688</v>
+        <v>8.439121794222345</v>
       </c>
       <c r="N4" t="n">
-        <v>121.6662202612054</v>
+        <v>121.5430690189354</v>
       </c>
       <c r="O4" t="n">
-        <v>11.03024116967555</v>
+        <v>11.02465731979617</v>
       </c>
       <c r="P4" t="n">
-        <v>246.8558752478936</v>
+        <v>246.6518863488161</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -18643,28 +18803,28 @@
         <v>0.0204</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.3710958603979377</v>
+        <v>-0.3284176831361804</v>
       </c>
       <c r="J5" t="n">
-        <v>421</v>
+        <v>425</v>
       </c>
       <c r="K5" t="n">
-        <v>420</v>
+        <v>424</v>
       </c>
       <c r="L5" t="n">
-        <v>0.04671003379692706</v>
+        <v>0.03683748124164965</v>
       </c>
       <c r="M5" t="n">
-        <v>9.911725361009502</v>
+        <v>9.999460007653052</v>
       </c>
       <c r="N5" t="n">
-        <v>154.9398778030764</v>
+        <v>157.3972323676327</v>
       </c>
       <c r="O5" t="n">
-        <v>12.44748479826653</v>
+        <v>12.54580536943056</v>
       </c>
       <c r="P5" t="n">
-        <v>230.820770949702</v>
+        <v>230.386043591303</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -18721,28 +18881,28 @@
         <v>0.0161</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.4177024506363475</v>
+        <v>-0.4235964918473271</v>
       </c>
       <c r="J6" t="n">
-        <v>421</v>
+        <v>425</v>
       </c>
       <c r="K6" t="n">
-        <v>419</v>
+        <v>423</v>
       </c>
       <c r="L6" t="n">
-        <v>0.04322236769104237</v>
+        <v>0.04530273183584121</v>
       </c>
       <c r="M6" t="n">
-        <v>10.88050520134215</v>
+        <v>10.80773205902296</v>
       </c>
       <c r="N6" t="n">
-        <v>209.8461367048133</v>
+        <v>208.0294454994924</v>
       </c>
       <c r="O6" t="n">
-        <v>14.48606698537644</v>
+        <v>14.42322590475142</v>
       </c>
       <c r="P6" t="n">
-        <v>210.9519003915493</v>
+        <v>211.0125507052913</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -18799,28 +18959,28 @@
         <v>0.016</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.06457200951448913</v>
+        <v>-0.05446929068696386</v>
       </c>
       <c r="J7" t="n">
-        <v>421</v>
+        <v>425</v>
       </c>
       <c r="K7" t="n">
-        <v>421</v>
+        <v>425</v>
       </c>
       <c r="L7" t="n">
-        <v>0.001910694460706686</v>
+        <v>0.001387215255331253</v>
       </c>
       <c r="M7" t="n">
-        <v>8.305229817558949</v>
+        <v>8.271623318256877</v>
       </c>
       <c r="N7" t="n">
-        <v>119.9369319003038</v>
+        <v>119.0749639537137</v>
       </c>
       <c r="O7" t="n">
-        <v>10.9515721200339</v>
+        <v>10.91214754086993</v>
       </c>
       <c r="P7" t="n">
-        <v>215.0918529450863</v>
+        <v>214.9888979470387</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -18858,7 +19018,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H422"/>
+  <dimension ref="A1:H426"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -36452,7 +36612,7 @@
       </c>
       <c r="E421" t="inlineStr">
         <is>
-          <t>-46.54275835541209,169.6138670867553</t>
+          <t>-46.54276871940327,169.61393450242386</t>
         </is>
       </c>
       <c r="F421" t="inlineStr">
@@ -36494,7 +36654,7 @@
       </c>
       <c r="E422" t="inlineStr">
         <is>
-          <t>-46.54275724079185,169.61385983639263</t>
+          <t>-46.54277816428945,169.61399593974602</t>
         </is>
       </c>
       <c r="F422" t="inlineStr">
@@ -36508,6 +36668,174 @@
         </is>
       </c>
       <c r="H422" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-22 22:14:08+00:00</t>
+        </is>
+      </c>
+      <c r="B423" t="inlineStr">
+        <is>
+          <t>-46.54105295880055,169.615123408322</t>
+        </is>
+      </c>
+      <c r="C423" t="inlineStr">
+        <is>
+          <t>-46.541617593206915,169.6146796663829</t>
+        </is>
+      </c>
+      <c r="D423" t="inlineStr">
+        <is>
+          <t>-46.54219142957629,169.61429582939957</t>
+        </is>
+      </c>
+      <c r="E423" t="inlineStr">
+        <is>
+          <t>-46.54278121480475,169.61401578286123</t>
+        </is>
+      </c>
+      <c r="F423" t="inlineStr">
+        <is>
+          <t>-46.54330921837906,169.61333390741993</t>
+        </is>
+      </c>
+      <c r="G423" t="inlineStr">
+        <is>
+          <t>-46.543952609257175,169.61340263972133</t>
+        </is>
+      </c>
+      <c r="H423" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-29 22:20:17+00:00</t>
+        </is>
+      </c>
+      <c r="B424" t="inlineStr">
+        <is>
+          <t>-46.541044140187495,169.61506604299774</t>
+        </is>
+      </c>
+      <c r="C424" t="inlineStr">
+        <is>
+          <t>-46.541613584655316,169.61465359099887</t>
+        </is>
+      </c>
+      <c r="D424" t="inlineStr">
+        <is>
+          <t>-46.54218945459209,169.61428298238243</t>
+        </is>
+      </c>
+      <c r="E424" t="inlineStr">
+        <is>
+          <t>-46.54278141035048,169.61401705485588</t>
+        </is>
+      </c>
+      <c r="F424" t="inlineStr">
+        <is>
+          <t>-46.54329852161083,169.6132643288044</t>
+        </is>
+      </c>
+      <c r="G424" t="inlineStr">
+        <is>
+          <t>-46.54395270703316,169.61340327573114</t>
+        </is>
+      </c>
+      <c r="H424" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-30 22:14:17+00:00</t>
+        </is>
+      </c>
+      <c r="B425" t="inlineStr">
+        <is>
+          <t>-46.541044140187495,169.61506604299774</t>
+        </is>
+      </c>
+      <c r="C425" t="inlineStr">
+        <is>
+          <t>-46.54161237231171,169.61464570478597</t>
+        </is>
+      </c>
+      <c r="D425" t="inlineStr">
+        <is>
+          <t>-46.54219090161036,169.61429239504835</t>
+        </is>
+      </c>
+      <c r="E425" t="inlineStr">
+        <is>
+          <t>-46.54277697145883,169.61398818057984</t>
+        </is>
+      </c>
+      <c r="F425" t="inlineStr">
+        <is>
+          <t>-46.54329852161083,169.6132643288044</t>
+        </is>
+      </c>
+      <c r="G425" t="inlineStr">
+        <is>
+          <t>-46.543952374594795,169.61340111329778</t>
+        </is>
+      </c>
+      <c r="H425" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-15 22:19:54+00:00</t>
+        </is>
+      </c>
+      <c r="B426" t="inlineStr">
+        <is>
+          <t>-46.54104771847514,169.61508931983423</t>
+        </is>
+      </c>
+      <c r="C426" t="inlineStr">
+        <is>
+          <t>-46.54161487521403,169.6146619860001</t>
+        </is>
+      </c>
+      <c r="D426" t="inlineStr">
+        <is>
+          <t>-46.54219430405572,169.6143145275352</t>
+        </is>
+      </c>
+      <c r="E426" t="inlineStr">
+        <is>
+          <t>-46.542783835116474,169.61403282759034</t>
+        </is>
+      </c>
+      <c r="F426" t="inlineStr">
+        <is>
+          <t>-46.543310665470635,169.61334332025135</t>
+        </is>
+      </c>
+      <c r="G426" t="inlineStr">
+        <is>
+          <t>-46.54395704828338,169.6134315145693</t>
+        </is>
+      </c>
+      <c r="H426" t="inlineStr">
         <is>
           <t>L8</t>
         </is>

--- a/data/nzd0543/nzd0543.xlsx
+++ b/data/nzd0543/nzd0543.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H426"/>
+  <dimension ref="A1:H428"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13086,7 +13086,7 @@
         <v>239.68</v>
       </c>
       <c r="F423" t="n">
-        <v>199.41</v>
+        <v>188.85</v>
       </c>
       <c r="G423" t="n">
         <v>218.15</v>
@@ -13116,7 +13116,7 @@
         <v>239.78</v>
       </c>
       <c r="F424" t="n">
-        <v>193.94</v>
+        <v>181.56</v>
       </c>
       <c r="G424" t="n">
         <v>218.2</v>
@@ -13146,7 +13146,7 @@
         <v>237.51</v>
       </c>
       <c r="F425" t="n">
-        <v>193.94</v>
+        <v>181.56</v>
       </c>
       <c r="G425" t="n">
         <v>218.03</v>
@@ -13176,7 +13176,7 @@
         <v>241.02</v>
       </c>
       <c r="F426" t="n">
-        <v>200.15</v>
+        <v>184.69</v>
       </c>
       <c r="G426" t="n">
         <v>220.42</v>
@@ -13184,6 +13184,66 @@
       <c r="H426" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-16 22:19:59+00:00</t>
+        </is>
+      </c>
+      <c r="B427" t="n">
+        <v>281.17</v>
+      </c>
+      <c r="C427" t="n">
+        <v>259.5</v>
+      </c>
+      <c r="D427" t="n">
+        <v>249.83</v>
+      </c>
+      <c r="E427" t="n">
+        <v>241.02</v>
+      </c>
+      <c r="F427" t="n">
+        <v>184.69</v>
+      </c>
+      <c r="G427" t="n">
+        <v>220.42</v>
+      </c>
+      <c r="H427" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-24 22:20:14+00:00</t>
+        </is>
+      </c>
+      <c r="B428" t="n">
+        <v>278.67</v>
+      </c>
+      <c r="C428" t="n">
+        <v>257.71</v>
+      </c>
+      <c r="D428" t="n">
+        <v>250.62</v>
+      </c>
+      <c r="E428" t="n">
+        <v>250.1</v>
+      </c>
+      <c r="F428" t="n">
+        <v>221.83</v>
+      </c>
+      <c r="G428" t="n">
+        <v>216.71</v>
+      </c>
+      <c r="H428" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -13198,7 +13258,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B520"/>
+  <dimension ref="A1:B523"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18401,6 +18461,36 @@
       </c>
       <c r="B520" t="n">
         <v>-0.23</v>
+      </c>
+    </row>
+    <row r="521">
+      <c r="A521" t="inlineStr">
+        <is>
+          <t>2026-06-16 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B521" t="n">
+        <v>-1.08</v>
+      </c>
+    </row>
+    <row r="522">
+      <c r="A522" t="inlineStr">
+        <is>
+          <t>2026-06-17 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B522" t="n">
+        <v>-0.9399999999999999</v>
+      </c>
+    </row>
+    <row r="523">
+      <c r="A523" t="inlineStr">
+        <is>
+          <t>2026-06-24 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B523" t="n">
+        <v>0.61</v>
       </c>
     </row>
   </sheetData>
@@ -18569,28 +18659,28 @@
         <v>0.0317</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.2625149074113793</v>
+        <v>-0.2600491346612403</v>
       </c>
       <c r="J2" t="n">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="K2" t="n">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="L2" t="n">
-        <v>0.03017853447369723</v>
+        <v>0.02993424674535894</v>
       </c>
       <c r="M2" t="n">
-        <v>8.709209139105356</v>
+        <v>8.677684734805073</v>
       </c>
       <c r="N2" t="n">
-        <v>124.2573499478782</v>
+        <v>123.7032632392023</v>
       </c>
       <c r="O2" t="n">
-        <v>11.14707809014892</v>
+        <v>11.12219687108632</v>
       </c>
       <c r="P2" t="n">
-        <v>284.2894174017837</v>
+        <v>284.2641041349399</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -18647,28 +18737,28 @@
         <v>0.0256</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.4489038859990397</v>
+        <v>-0.4458740230519838</v>
       </c>
       <c r="J3" t="n">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="K3" t="n">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="L3" t="n">
-        <v>0.08088274186569389</v>
+        <v>0.08065351620999306</v>
       </c>
       <c r="M3" t="n">
-        <v>8.764775374122062</v>
+        <v>8.738087981847315</v>
       </c>
       <c r="N3" t="n">
-        <v>127.2017848475874</v>
+        <v>126.6525502199607</v>
       </c>
       <c r="O3" t="n">
-        <v>11.2783768711454</v>
+        <v>11.25400152034647</v>
       </c>
       <c r="P3" t="n">
-        <v>267.3319972143256</v>
+        <v>267.3008011433583</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -18725,28 +18815,28 @@
         <v>0.0259</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.3209041048073187</v>
+        <v>-0.3094631470120401</v>
       </c>
       <c r="J4" t="n">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="K4" t="n">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="L4" t="n">
-        <v>0.04539584538247987</v>
+        <v>0.04256236070302732</v>
       </c>
       <c r="M4" t="n">
-        <v>8.439121794222345</v>
+        <v>8.461183699358921</v>
       </c>
       <c r="N4" t="n">
-        <v>121.5430690189354</v>
+        <v>121.6494073657323</v>
       </c>
       <c r="O4" t="n">
-        <v>11.02465731979617</v>
+        <v>11.02947901606111</v>
       </c>
       <c r="P4" t="n">
-        <v>246.6518863488161</v>
+        <v>246.5347715630069</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -18803,28 +18893,28 @@
         <v>0.0204</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.3284176831361804</v>
+        <v>-0.3057894819837064</v>
       </c>
       <c r="J5" t="n">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="K5" t="n">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="L5" t="n">
-        <v>0.03683748124164965</v>
+        <v>0.03189301357024776</v>
       </c>
       <c r="M5" t="n">
-        <v>9.999460007653052</v>
+        <v>10.04707608552377</v>
       </c>
       <c r="N5" t="n">
-        <v>157.3972323676327</v>
+        <v>159.3932878683614</v>
       </c>
       <c r="O5" t="n">
-        <v>12.54580536943056</v>
+        <v>12.62510545969266</v>
       </c>
       <c r="P5" t="n">
-        <v>230.386043591303</v>
+        <v>230.1540829625249</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -18881,28 +18971,28 @@
         <v>0.0161</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.4235964918473271</v>
+        <v>-0.4442832445480021</v>
       </c>
       <c r="J6" t="n">
+        <v>427</v>
+      </c>
+      <c r="K6" t="n">
         <v>425</v>
       </c>
-      <c r="K6" t="n">
-        <v>423</v>
-      </c>
       <c r="L6" t="n">
-        <v>0.04530273183584121</v>
+        <v>0.0492518237913131</v>
       </c>
       <c r="M6" t="n">
-        <v>10.80773205902296</v>
+        <v>10.96052626271742</v>
       </c>
       <c r="N6" t="n">
-        <v>208.0294454994924</v>
+        <v>210.9271137816152</v>
       </c>
       <c r="O6" t="n">
-        <v>14.42322590475142</v>
+        <v>14.52332998253552</v>
       </c>
       <c r="P6" t="n">
-        <v>211.0125507052913</v>
+        <v>211.2252143231336</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -18959,28 +19049,28 @@
         <v>0.016</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.05446929068696386</v>
+        <v>-0.04971684052674785</v>
       </c>
       <c r="J7" t="n">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="K7" t="n">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="L7" t="n">
-        <v>0.001387215255331253</v>
+        <v>0.001167265775299353</v>
       </c>
       <c r="M7" t="n">
-        <v>8.271623318256877</v>
+        <v>8.253631702021474</v>
       </c>
       <c r="N7" t="n">
-        <v>119.0749639537137</v>
+        <v>118.6495524477347</v>
       </c>
       <c r="O7" t="n">
-        <v>10.91214754086993</v>
+        <v>10.89263753402888</v>
       </c>
       <c r="P7" t="n">
-        <v>214.9888979470387</v>
+        <v>214.9402033024798</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -19018,7 +19108,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H426"/>
+  <dimension ref="A1:H428"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -36701,7 +36791,7 @@
       </c>
       <c r="F423" t="inlineStr">
         <is>
-          <t>-46.54330921837906,169.61333390741993</t>
+          <t>-46.5432885679079,169.6131995838305</t>
         </is>
       </c>
       <c r="G423" t="inlineStr">
@@ -36743,7 +36833,7 @@
       </c>
       <c r="F424" t="inlineStr">
         <is>
-          <t>-46.54329852161083,169.6132643288044</t>
+          <t>-46.54327431195226,169.61310685482607</t>
         </is>
       </c>
       <c r="G424" t="inlineStr">
@@ -36785,7 +36875,7 @@
       </c>
       <c r="F425" t="inlineStr">
         <is>
-          <t>-46.54329852161083,169.6132643288044</t>
+          <t>-46.54327431195226,169.61310685482607</t>
         </is>
       </c>
       <c r="G425" t="inlineStr">
@@ -36827,7 +36917,7 @@
       </c>
       <c r="F426" t="inlineStr">
         <is>
-          <t>-46.543310665470635,169.61334332025135</t>
+          <t>-46.54328043283116,169.6131466685074</t>
         </is>
       </c>
       <c r="G426" t="inlineStr">
@@ -36838,6 +36928,90 @@
       <c r="H426" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-16 22:19:59+00:00</t>
+        </is>
+      </c>
+      <c r="B427" t="inlineStr">
+        <is>
+          <t>-46.541042047962506,169.61505243304572</t>
+        </is>
+      </c>
+      <c r="C427" t="inlineStr">
+        <is>
+          <t>-46.54160644746358,169.61460716410585</t>
+        </is>
+      </c>
+      <c r="D427" t="inlineStr">
+        <is>
+          <t>-46.54219430405572,169.6143145275352</t>
+        </is>
+      </c>
+      <c r="E427" t="inlineStr">
+        <is>
+          <t>-46.542783835116474,169.61403282759034</t>
+        </is>
+      </c>
+      <c r="F427" t="inlineStr">
+        <is>
+          <t>-46.54328043283116,169.6131466685074</t>
+        </is>
+      </c>
+      <c r="G427" t="inlineStr">
+        <is>
+          <t>-46.54395704828338,169.6134315145693</t>
+        </is>
+      </c>
+      <c r="H427" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-24 22:20:14+00:00</t>
+        </is>
+      </c>
+      <c r="B428" t="inlineStr">
+        <is>
+          <t>-46.54103715958014,169.61502063409682</t>
+        </is>
+      </c>
+      <c r="C428" t="inlineStr">
+        <is>
+          <t>-46.54160294729976,169.61458439585357</t>
+        </is>
+      </c>
+      <c r="D428" t="inlineStr">
+        <is>
+          <t>-46.542195848842724,169.61432457619406</t>
+        </is>
+      </c>
+      <c r="E428" t="inlineStr">
+        <is>
+          <t>-46.542801590595666,169.61414832475663</t>
+        </is>
+      </c>
+      <c r="F428" t="inlineStr">
+        <is>
+          <t>-46.54335306100452,169.61361909101282</t>
+        </is>
+      </c>
+      <c r="G428" t="inlineStr">
+        <is>
+          <t>-46.54394979330731,169.61338432263977</t>
+        </is>
+      </c>
+      <c r="H428" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
